--- a/TestDataFile/WebOrder_Order_Data.xlsx
+++ b/TestDataFile/WebOrder_Order_Data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Training_Scripts\Selenium Training Data\WebOrder_POM_TestNG_Demo\TestDataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA70335-C45C-45D4-8C74-C75732B0EC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F14DB80-00B8-474F-B16D-DCBA9A9D13CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orders" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="36">
   <si>
     <t>product</t>
   </si>
@@ -162,7 +163,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -170,14 +171,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -992,4 +1010,550 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F7CEE6-8D9E-4A61-926C-0085CE42D587}">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3">
+        <v>10101</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J2" s="4">
+        <v>47453</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3">
+        <v>90909</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J3" s="4">
+        <v>47454</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10101</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J4" s="4">
+        <v>47455</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3">
+        <v>90909</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J5" s="4">
+        <v>47456</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="3">
+        <v>10101</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J6" s="4">
+        <v>47457</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3">
+        <v>10101</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J7" s="4">
+        <v>47458</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="3">
+        <v>90909</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J8" s="4">
+        <v>47459</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J9" s="4">
+        <v>47460</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
+        <v>231232</v>
+      </c>
+      <c r="J10" s="4">
+        <v>47461</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="3">
+        <v>10101</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="4">
+        <v>47462</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="3">
+        <v>90909</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="4">
+        <v>47463</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="3">
+        <v>10101</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="3">
+        <v>213213</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="3">
+        <v>10101</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2132131</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3">
+        <v>34</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="3">
+        <v>90909</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="3">
+        <v>123213123</v>
+      </c>
+      <c r="J15" s="4">
+        <v>47463</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestDataFile/WebOrder_Order_Data.xlsx
+++ b/TestDataFile/WebOrder_Order_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Training_Scripts\Selenium Training Data\WebOrder_POM_TestNG_Demo\TestDataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F14DB80-00B8-474F-B16D-DCBA9A9D13CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE61C08-6B9F-4100-9023-52DB8F80FCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="37">
   <si>
     <t>product</t>
   </si>
@@ -134,13 +134,16 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>12/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +153,22 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -190,12 +209,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,532 +515,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="6">
         <v>10101</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2">
-        <v>231232</v>
-      </c>
-      <c r="J2" s="2">
-        <v>47453</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="6">
         <v>90909</v>
       </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3">
-        <v>231232</v>
-      </c>
-      <c r="J3" s="2">
-        <v>47454</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="H3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="6">
         <v>10101</v>
       </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4">
-        <v>231232</v>
-      </c>
-      <c r="J4" s="2">
-        <v>47455</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="H4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>0</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="6">
         <v>90909</v>
       </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5">
-        <v>231232</v>
-      </c>
-      <c r="J5" s="2">
-        <v>47456</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="H5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="6">
         <v>10101</v>
       </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6">
-        <v>231232</v>
-      </c>
-      <c r="J6" s="2">
-        <v>47457</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="6">
         <v>10101</v>
       </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7">
-        <v>231232</v>
-      </c>
-      <c r="J7" s="2">
-        <v>47458</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="H7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8">
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="6">
         <v>90909</v>
       </c>
-      <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8">
-        <v>231232</v>
-      </c>
-      <c r="J8" s="2">
-        <v>47459</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="H8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9">
-        <v>231232</v>
-      </c>
-      <c r="J9" s="2">
-        <v>47460</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="F9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="4">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10">
-        <v>231232</v>
-      </c>
-      <c r="J10" s="2">
-        <v>47461</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="H10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="6">
+        <v>231232</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
+      <c r="F11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="6">
         <v>10101</v>
       </c>
-      <c r="H11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="2">
-        <v>47462</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="H11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
+      <c r="F12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="6">
         <v>90909</v>
       </c>
-      <c r="H12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="2">
-        <v>47463</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="J12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
         <v>1</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
+      <c r="F13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="6">
         <v>10101</v>
       </c>
-      <c r="H13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13">
+      <c r="H13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="6">
         <v>213213</v>
       </c>
-      <c r="J13" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="J13" s="8"/>
+      <c r="K13" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14">
+      <c r="F14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="6">
         <v>10101</v>
       </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14">
+      <c r="H14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="6">
         <v>2132131</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="4">
         <v>34</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15">
+      <c r="F15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="6">
         <v>90909</v>
       </c>
-      <c r="H15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15">
+      <c r="H15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="6">
         <v>123213123</v>
       </c>
-      <c r="J15" s="2">
-        <v>47463</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="J15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1031,525 +1066,525 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1">
         <v>10101</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J2" s="4">
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J2" s="2">
         <v>47453</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="1">
         <v>34</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1">
         <v>90909</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J3" s="4">
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J3" s="2">
         <v>47454</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1">
         <v>10101</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J4" s="4">
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J4" s="2">
         <v>47455</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1">
         <v>90909</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="H5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J5" s="2">
         <v>47456</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="1">
         <v>10101</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J6" s="4">
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J6" s="2">
         <v>47457</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1">
         <v>10101</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J7" s="4">
+      <c r="H7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J7" s="2">
         <v>47458</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="1">
         <v>90909</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J8" s="4">
+      <c r="H8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J8" s="2">
         <v>47459</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="F9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J9" s="4">
+      <c r="H9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J9" s="2">
         <v>47460</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="1">
         <v>34</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="F10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="3">
-        <v>231232</v>
-      </c>
-      <c r="J10" s="4">
+      <c r="H10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="1">
+        <v>231232</v>
+      </c>
+      <c r="J10" s="2">
         <v>47461</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="F11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="1">
         <v>10101</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="2">
         <v>47462</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="1">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1">
         <v>90909</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="2">
         <v>47463</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="1">
         <v>10101</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="H13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="1">
         <v>213213</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="1">
         <v>10101</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="1">
         <v>2132131</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="1">
         <v>34</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="F15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="1">
         <v>90909</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="H15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1">
         <v>123213123</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="2">
         <v>47463</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="1" t="s">
         <v>31</v>
       </c>
     </row>
